--- a/resources/Part_3_Statistics/S18_L112/3.13.Confidence-intervals.Two-means.Dependent-samples-exercise.xlsx
+++ b/resources/Part_3_Statistics/S18_L112/3.13.Confidence-intervals.Two-means.Dependent-samples-exercise.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18229"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data in lbs" sheetId="1" r:id="rId1"/>
     <sheet name="Data in kg" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="38">
   <si>
     <t>Confidence interval for difference of two means, dependent samples</t>
   </si>
@@ -89,6 +89,51 @@
   </si>
   <si>
     <t>Weight after (kg)</t>
+  </si>
+  <si>
+    <t>Task 1:</t>
+  </si>
+  <si>
+    <t>Mean =</t>
+  </si>
+  <si>
+    <t>Std Dev=</t>
+  </si>
+  <si>
+    <t>(xi-mean)^2</t>
+  </si>
+  <si>
+    <t>task 2:</t>
+  </si>
+  <si>
+    <t>Use T-statistics, 9 degrees of liberty, Unknown population Standard deviation</t>
+  </si>
+  <si>
+    <t>Task 3:</t>
+  </si>
+  <si>
+    <t>95% confidence interval</t>
+  </si>
+  <si>
+    <t>from:</t>
+  </si>
+  <si>
+    <t>alpha: 5%</t>
+  </si>
+  <si>
+    <t>alpha/2-&gt;</t>
+  </si>
+  <si>
+    <t>alpha/2= 2,262</t>
+  </si>
+  <si>
+    <t>to:</t>
+  </si>
+  <si>
+    <t>Task 4:</t>
+  </si>
+  <si>
+    <t>You are 95% certain that if you start the program you will have lost a minimum of 6,86Kg and at most 11,31Kg if you complete the program.</t>
   </si>
 </sst>
 </file>
@@ -496,36 +541,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:O25"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="1"/>
-    <col min="8" max="8" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="10.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="1"/>
+    <col min="8" max="8" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.5703125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
@@ -533,13 +578,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
       <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
@@ -547,7 +592,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
@@ -555,7 +600,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
@@ -563,7 +608,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
@@ -571,7 +616,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
@@ -579,13 +624,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="3"/>
     </row>
-    <row r="14" spans="2:11" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
         <v>5</v>
       </c>
@@ -600,7 +645,7 @@
       </c>
       <c r="F14" s="12"/>
     </row>
-    <row r="15" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="1">
         <v>1</v>
       </c>
@@ -620,7 +665,7 @@
       <c r="I15" s="5"/>
       <c r="K15" s="3"/>
     </row>
-    <row r="16" spans="2:11" ht="12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
         <v>2</v>
       </c>
@@ -638,7 +683,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="5"/>
     </row>
-    <row r="17" spans="2:15" ht="12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="1">
         <v>3</v>
       </c>
@@ -656,7 +701,7 @@
       <c r="K17" s="3"/>
       <c r="L17" s="5"/>
     </row>
-    <row r="18" spans="2:15" ht="12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="1">
         <v>4</v>
       </c>
@@ -674,7 +719,7 @@
       <c r="G18" s="3"/>
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="2:15" ht="12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" s="1">
         <v>5</v>
       </c>
@@ -696,7 +741,7 @@
       <c r="M19" s="12"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="2:15" ht="12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="1">
         <v>6</v>
       </c>
@@ -757,7 +802,7 @@
       <c r="N22" s="10"/>
       <c r="O22" s="10"/>
     </row>
-    <row r="23" spans="2:15" ht="12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
         <v>9</v>
       </c>
@@ -813,36 +858,36 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:R28"/>
-  <sheetFormatPr defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:S28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="9.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="1"/>
-    <col min="8" max="8" width="11.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="33.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5546875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="10.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="9.42578125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="1"/>
+    <col min="8" max="8" width="11.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
@@ -850,13 +895,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
@@ -864,7 +909,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
@@ -872,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
@@ -880,7 +925,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>12</v>
       </c>
@@ -888,7 +933,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
@@ -896,13 +941,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B12" s="3"/>
     </row>
-    <row r="14" spans="2:18" ht="12.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:19" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
         <v>5</v>
       </c>
@@ -916,8 +961,20 @@
         <v>1</v>
       </c>
       <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+      <c r="G14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B15" s="1">
         <v>1</v>
       </c>
@@ -932,10 +989,18 @@
         <v>-10.809999990934841</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="G15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="15">
+        <f>SUM(E15:E24)/COUNT(E15:E24)</f>
+        <v>-9.0829999923830833</v>
+      </c>
       <c r="I15" s="11"/>
-      <c r="J15" s="10"/>
+      <c r="J15" s="10">
+        <f>(E15-$H$15)^2</f>
+        <v>2.9825289949977716</v>
+      </c>
       <c r="K15" s="15"/>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
@@ -945,7 +1010,7 @@
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
     </row>
-    <row r="16" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
         <v>2</v>
       </c>
@@ -960,20 +1025,43 @@
         <v>-9.0999999923688506</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="15"/>
+      <c r="G16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="15">
+        <f>SQRT(SUM(J15:J24)/(COUNT(E15:E24)-1))</f>
+        <v>3.1111414456558117</v>
+      </c>
       <c r="I16" s="11"/>
-      <c r="J16" s="10"/>
+      <c r="J16" s="10">
+        <f t="shared" ref="J16:J24" si="1">(E16-$H$15)^2</f>
+        <v>2.889999995160878E-4</v>
+      </c>
       <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+      <c r="L16" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-    </row>
-    <row r="17" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+      <c r="O16" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="10">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" s="1">
         <v>3</v>
       </c>
@@ -988,20 +1076,36 @@
         <v>-13.389999988771265</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="10"/>
+      <c r="G17" s="10">
+        <f>_xlfn.STDEV.S(E15:E24)</f>
+        <v>3.1111414456558117</v>
+      </c>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
+      <c r="J17" s="10">
+        <f t="shared" si="1"/>
+        <v>18.5502489688878</v>
+      </c>
       <c r="K17" s="15"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
+      <c r="L17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17" s="10">
+        <f>H15-2.262*H16/SQRT(COUNT(E15:E24))</f>
+        <v>-11.308421889617348</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="O17" s="10">
+        <f>H15+2.262*H16/SQRT(COUNT(E15:E24))</f>
+        <v>-6.8575780951488188</v>
+      </c>
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
     </row>
-    <row r="18" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" s="1">
         <v>4</v>
       </c>
@@ -1019,7 +1123,10 @@
       <c r="G18" s="15"/>
       <c r="H18" s="16"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
+      <c r="J18" s="10">
+        <f t="shared" si="1"/>
+        <v>12.341168979301598</v>
+      </c>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
       <c r="M18" s="10"/>
@@ -1029,7 +1136,7 @@
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
     </row>
-    <row r="19" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" s="1">
         <v>5</v>
       </c>
@@ -1047,7 +1154,10 @@
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
+      <c r="J19" s="10">
+        <f t="shared" si="1"/>
+        <v>19.035768968073608</v>
+      </c>
       <c r="K19" s="12"/>
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
@@ -1057,7 +1167,7 @@
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
     </row>
-    <row r="20" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B20" s="1">
         <v>6</v>
       </c>
@@ -1075,10 +1185,17 @@
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
+      <c r="J20" s="10">
+        <f t="shared" si="1"/>
+        <v>8.7202089853746845</v>
+      </c>
       <c r="K20" s="14"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
+      <c r="L20" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>37</v>
+      </c>
       <c r="N20" s="10"/>
       <c r="O20" s="10"/>
       <c r="P20" s="10"/>
@@ -1103,7 +1220,10 @@
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
+      <c r="J21" s="10">
+        <f t="shared" si="1"/>
+        <v>0.64480899891855092</v>
+      </c>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
       <c r="M21" s="10"/>
@@ -1131,7 +1251,10 @@
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
+      <c r="J22" s="10">
+        <f t="shared" si="1"/>
+        <v>0.81540899863241645</v>
+      </c>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
       <c r="M22" s="10"/>
@@ -1141,7 +1264,7 @@
       <c r="Q22" s="10"/>
       <c r="R22" s="10"/>
     </row>
-    <row r="23" spans="2:18" ht="12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
         <v>9</v>
       </c>
@@ -1159,7 +1282,10 @@
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
+      <c r="J23" s="10">
+        <f t="shared" si="1"/>
+        <v>4.0682889931767292</v>
+      </c>
       <c r="K23" s="15"/>
       <c r="L23" s="10"/>
       <c r="M23" s="10"/>
@@ -1187,7 +1313,10 @@
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
+      <c r="J24" s="10">
+        <f t="shared" si="1"/>
+        <v>19.954088966533359</v>
+      </c>
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
       <c r="M24" s="10"/>
